--- a/outputs/37900.xlsx
+++ b/outputs/37900.xlsx
@@ -134,27 +134,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -436,7 +436,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A4:G16"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.86"/>
@@ -471,8 +471,8 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">VLOOKUP(E4,A5:B16,2,TRUE())</f>
-        <v>2000</v>
+        <f aca="false">VLOOKUP(DATE(2024,MONTH(E4),1),A5:B16,2,FALSE())</f>
+        <v>5000</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>

--- a/outputs/37900.xlsx
+++ b/outputs/37900.xlsx
@@ -129,7 +129,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -148,6 +148,10 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -446,7 +450,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -460,7 +464,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
@@ -471,13 +475,13 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">VLOOKUP(DATE(2024,MONTH(E4),1),A5:B16,2,FALSE())</f>
-        <v>5000</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">INDEX($B$5:$B$16,MATCH(MAX($A$5:$A$16,$A$5:$A$16&lt;=$E$4),$A$5:$A$16,0))</f>
+        <v>2000</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>45323</v>
       </c>
@@ -485,7 +489,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>45352</v>
       </c>
@@ -493,7 +497,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>45383</v>
       </c>
@@ -501,7 +505,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
         <v>45413</v>
       </c>
@@ -509,7 +513,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
         <v>45444</v>
       </c>
@@ -517,7 +521,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
         <v>45474</v>
       </c>
@@ -525,7 +529,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>45505</v>
       </c>
@@ -533,7 +537,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>45536</v>
       </c>
@@ -541,7 +545,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>45566</v>
       </c>
@@ -549,7 +553,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>45597</v>
       </c>
@@ -557,7 +561,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>45627</v>
       </c>
